--- a/Archives/Data/S2-S3 vf/S3_2050/extensions/imp_biogeochemical/detail_levels.xlsx
+++ b/Archives/Data/S2-S3 vf/S3_2050/extensions/imp_biogeochemical/detail_levels.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N2O - agriculture - air</t>
+          <t>Pxx - agriculture - soil</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NH3 - agriculture - air</t>
+          <t>N - waste - water</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>P - waste - water</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NH3 - combustion - air</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NH3 - non combustion - N- fertilizer production - air</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>N2O - agriculture - air</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NH3 - agriculture - air</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>NOX - agriculture - air</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NH3 - waste - air</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NOX - waste - air</t>
         </is>
       </c>
     </row>
